--- a/Analysed/GPT_gpt-5.3-chat-latest_cot.xlsx
+++ b/Analysed/GPT_gpt-5.3-chat-latest_cot.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J54"/>
+  <dimension ref="A1:J55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -514,16 +514,16 @@
         </is>
       </c>
       <c r="G2" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H2" t="n">
-        <v>4.589384615384616</v>
+        <v>4.620909090909092</v>
       </c>
       <c r="I2" t="n">
-        <v>5.463197851920683</v>
+        <v>5.483464675593784</v>
       </c>
       <c r="J2" t="n">
-        <v>0.171875</v>
+        <v>0.1692307692307692</v>
       </c>
     </row>
     <row r="3">
@@ -693,10 +693,10 @@
         <v>11</v>
       </c>
       <c r="H6" t="n">
-        <v>1.665454545454545</v>
+        <v>1.667272727272727</v>
       </c>
       <c r="I6" t="n">
-        <v>1.956095368561843</v>
+        <v>1.957038579078093</v>
       </c>
       <c r="J6" t="n">
         <v>0.2</v>
@@ -822,16 +822,16 @@
         </is>
       </c>
       <c r="G9" t="n">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="H9" t="n">
-        <v>0.4344444444444444</v>
+        <v>0.4232432432432432</v>
       </c>
       <c r="I9" t="n">
-        <v>0.597448277631164</v>
+        <v>0.5893285230735978</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6857142857142857</v>
+        <v>0.6944444444444444</v>
       </c>
     </row>
     <row r="10">
@@ -954,16 +954,16 @@
         </is>
       </c>
       <c r="G12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3608333333333333</v>
+        <v>0.3330769230769231</v>
       </c>
       <c r="I12" t="n">
-        <v>0.5300393067185364</v>
+        <v>0.5092452937738053</v>
       </c>
       <c r="J12" t="n">
-        <v>0.7272727272727273</v>
+        <v>0.75</v>
       </c>
     </row>
     <row r="13">
@@ -1570,16 +1570,16 @@
         </is>
       </c>
       <c r="G26" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="H26" t="n">
-        <v>3.246399999999996</v>
+        <v>3.28884615384615</v>
       </c>
       <c r="I26" t="n">
-        <v>3.352418828249236</v>
+        <v>3.396209991695491</v>
       </c>
       <c r="J26" t="n">
-        <v>0.1666666666666667</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="27">
@@ -1878,16 +1878,16 @@
         </is>
       </c>
       <c r="G33" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="H33" t="n">
-        <v>37.84857142857144</v>
+        <v>38.205</v>
       </c>
       <c r="I33" t="n">
-        <v>37.88959299257326</v>
+        <v>38.25218751914719</v>
       </c>
       <c r="J33" t="n">
-        <v>0.8333333333333334</v>
+        <v>0.8571428571428571</v>
       </c>
     </row>
     <row r="34">
@@ -2054,16 +2054,16 @@
         </is>
       </c>
       <c r="G37" t="n">
-        <v>21</v>
+        <v>30</v>
       </c>
       <c r="H37" t="n">
-        <v>2.159761904761904</v>
+        <v>1.771333333333332</v>
       </c>
       <c r="I37" t="n">
-        <v>2.309367311830748</v>
+        <v>1.994415118942559</v>
       </c>
       <c r="J37" t="n">
-        <v>0.3</v>
+        <v>0.2068965517241379</v>
       </c>
     </row>
     <row r="38">
@@ -2274,16 +2274,16 @@
         </is>
       </c>
       <c r="G42" t="n">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="H42" t="n">
-        <v>10.96130434782609</v>
+        <v>12.2684</v>
       </c>
       <c r="I42" t="n">
-        <v>14.26584702372585</v>
+        <v>15.71166572964178</v>
       </c>
       <c r="J42" t="n">
-        <v>0.2888888888888889</v>
+        <v>0.3469387755102041</v>
       </c>
     </row>
     <row r="43">
@@ -2318,16 +2318,16 @@
         </is>
       </c>
       <c r="G43" t="n">
-        <v>30</v>
+        <v>35</v>
       </c>
       <c r="H43" t="n">
-        <v>4.782333333333335</v>
+        <v>4.567714285714287</v>
       </c>
       <c r="I43" t="n">
-        <v>5.438868448491838</v>
+        <v>5.206113713702382</v>
       </c>
       <c r="J43" t="n">
-        <v>0.5862068965517241</v>
+        <v>0.5</v>
       </c>
     </row>
     <row r="44">
@@ -2402,20 +2402,20 @@
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G45" t="n">
-        <v>24</v>
+        <v>204</v>
       </c>
       <c r="H45" t="n">
-        <v>9.294166666666667</v>
+        <v>4.315049019607843</v>
       </c>
       <c r="I45" t="n">
-        <v>10.76840207892208</v>
+        <v>5.224565888711731</v>
       </c>
       <c r="J45" t="n">
-        <v>0.391304347826087</v>
+        <v>0.4334975369458128</v>
       </c>
     </row>
     <row r="46">
@@ -2446,20 +2446,20 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G46" t="n">
-        <v>90</v>
+        <v>24</v>
       </c>
       <c r="H46" t="n">
-        <v>7.243333333333333</v>
+        <v>9.294166666666667</v>
       </c>
       <c r="I46" t="n">
-        <v>8.588530077311768</v>
+        <v>10.76840207892208</v>
       </c>
       <c r="J46" t="n">
-        <v>0.3483146067415731</v>
+        <v>0.391304347826087</v>
       </c>
     </row>
     <row r="47">
@@ -2490,20 +2490,20 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G47" t="n">
-        <v>12</v>
+        <v>91</v>
       </c>
       <c r="H47" t="n">
-        <v>5.080833333333334</v>
+        <v>7.308791208791209</v>
       </c>
       <c r="I47" t="n">
-        <v>5.64712832626755</v>
+        <v>8.652571490984251</v>
       </c>
       <c r="J47" t="n">
-        <v>0.2727272727272727</v>
+        <v>0.3444444444444444</v>
       </c>
     </row>
     <row r="48">
@@ -2534,20 +2534,20 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V5_5 divisions_per_second</t>
         </is>
       </c>
       <c r="G48" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="H48" t="n">
-        <v>39.60777777777778</v>
+        <v>5.080833333333334</v>
       </c>
       <c r="I48" t="n">
-        <v>40.07636391246647</v>
+        <v>5.64712832626755</v>
       </c>
       <c r="J48" t="n">
-        <v>0.25</v>
+        <v>0.2727272727272727</v>
       </c>
     </row>
     <row r="49">
@@ -2573,25 +2573,25 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>OPENING</t>
+          <t>OPENING-CLOSING</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
+          <t>OPENING-CLOSING_OPENING-CLOSING_V6_10 divisions_per_second</t>
         </is>
       </c>
       <c r="G49" t="n">
-        <v>63</v>
+        <v>9</v>
       </c>
       <c r="H49" t="n">
-        <v>8.110476190476192</v>
+        <v>39.60777777777778</v>
       </c>
       <c r="I49" t="n">
-        <v>9.489755211187168</v>
+        <v>40.07636391246647</v>
       </c>
       <c r="J49" t="n">
-        <v>0.01612903225806452</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="50">
@@ -2622,20 +2622,20 @@
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
+          <t>OPENING_OPENING_V1_0.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G50" t="n">
-        <v>195</v>
+        <v>63</v>
       </c>
       <c r="H50" t="n">
-        <v>9.645282051282051</v>
+        <v>8.110476190476192</v>
       </c>
       <c r="I50" t="n">
-        <v>11.75257433883077</v>
+        <v>9.489755211187168</v>
       </c>
       <c r="J50" t="n">
-        <v>0.06701030927835051</v>
+        <v>0.01612903225806452</v>
       </c>
     </row>
     <row r="51">
@@ -2666,20 +2666,20 @@
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
+          <t>OPENING_OPENING_V2_0.8 divisions_per_second</t>
         </is>
       </c>
       <c r="G51" t="n">
-        <v>23</v>
+        <v>200</v>
       </c>
       <c r="H51" t="n">
-        <v>48.3</v>
+        <v>9.97415</v>
       </c>
       <c r="I51" t="n">
-        <v>49.28706806314278</v>
+        <v>12.15178704964829</v>
       </c>
       <c r="J51" t="n">
-        <v>0.8636363636363636</v>
+        <v>0.09045226130653267</v>
       </c>
     </row>
     <row r="52">
@@ -2710,20 +2710,20 @@
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
+          <t>OPENING_OPENING_V3_1.7 divisions_per_second</t>
         </is>
       </c>
       <c r="G52" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="H52" t="n">
-        <v>46.814375</v>
+        <v>48.3</v>
       </c>
       <c r="I52" t="n">
-        <v>47.65908471897042</v>
+        <v>49.28706806314278</v>
       </c>
       <c r="J52" t="n">
-        <v>0.8666666666666667</v>
+        <v>0.8636363636363636</v>
       </c>
     </row>
     <row r="53">
@@ -2754,20 +2754,20 @@
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+          <t>OPENING_OPENING_V4_2.5 divisions_per_second</t>
         </is>
       </c>
       <c r="G53" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="H53" t="n">
-        <v>15.306</v>
+        <v>47.59588235294117</v>
       </c>
       <c r="I53" t="n">
-        <v>17.63898183002636</v>
+        <v>48.47936110285671</v>
       </c>
       <c r="J53" t="n">
-        <v>0.7777777777777778</v>
+        <v>0.8125</v>
       </c>
     </row>
     <row r="54">
@@ -2798,19 +2798,63 @@
       </c>
       <c r="F54" t="inlineStr">
         <is>
+          <t>OPENING_OPENING_V5_5 divisions_per_second</t>
+        </is>
+      </c>
+      <c r="G54" t="n">
+        <v>11</v>
+      </c>
+      <c r="H54" t="n">
+        <v>14.26</v>
+      </c>
+      <c r="I54" t="n">
+        <v>16.85709130522604</v>
+      </c>
+      <c r="J54" t="n">
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>GPT</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gpt-5.3-chat-latest</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>cot</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>3.- Analog Depth Gauge_without vernier</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>OPENING</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
           <t>OPENING_OPENING_V6_10 divisions_per_second</t>
         </is>
       </c>
-      <c r="G54" t="n">
+      <c r="G55" t="n">
         <v>7</v>
       </c>
-      <c r="H54" t="n">
+      <c r="H55" t="n">
         <v>10.64285714285714</v>
       </c>
-      <c r="I54" t="n">
+      <c r="I55" t="n">
         <v>12.98206895243259</v>
       </c>
-      <c r="J54" t="n">
+      <c r="J55" t="n">
         <v>0.6666666666666666</v>
       </c>
     </row>
@@ -2857,14 +2901,14 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.5504</v>
+        <v>8.4946</v>
       </c>
       <c r="C2" t="n">
-        <v>12.4765</v>
+        <v>12.4355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8.5504 ± 12.4765</t>
+          <t>8.4946 ± 12.4355</t>
         </is>
       </c>
     </row>
@@ -2875,14 +2919,14 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>9.1922</v>
+        <v>9.151999999999999</v>
       </c>
       <c r="C3" t="n">
-        <v>12.6232</v>
+        <v>12.5883</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.1922 ± 12.6232</t>
+          <t>9.1520 ± 12.5883</t>
         </is>
       </c>
     </row>
@@ -2893,14 +2937,14 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4393</v>
+        <v>0.4365</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3008</v>
+        <v>0.2953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.4393 ± 0.3008</t>
+          <t>0.4365 ± 0.2953</t>
         </is>
       </c>
     </row>
@@ -2975,19 +3019,19 @@
         <v>6</v>
       </c>
       <c r="D2" t="n">
-        <v>1.9921</v>
+        <v>1.9977</v>
       </c>
       <c r="E2" t="n">
-        <v>1.354</v>
+        <v>1.3673</v>
       </c>
       <c r="F2" t="n">
-        <v>2.4101</v>
+        <v>2.4136</v>
       </c>
       <c r="G2" t="n">
-        <v>0.4349</v>
+        <v>0.4345</v>
       </c>
       <c r="H2" t="n">
-        <v>40.7</v>
+        <v>40.8</v>
       </c>
     </row>
     <row r="3">
@@ -3035,19 +3079,19 @@
         <v>6</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1326</v>
+        <v>1.1261</v>
       </c>
       <c r="E4" t="n">
-        <v>2.0461</v>
+        <v>2.0493</v>
       </c>
       <c r="F4" t="n">
-        <v>1.27</v>
+        <v>1.2652</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6036</v>
+        <v>0.6089</v>
       </c>
       <c r="H4" t="n">
-        <v>17.2</v>
+        <v>17.5</v>
       </c>
     </row>
     <row r="5">
@@ -3095,19 +3139,19 @@
         <v>6</v>
       </c>
       <c r="D6" t="n">
-        <v>8.569800000000001</v>
+        <v>8.564500000000001</v>
       </c>
       <c r="E6" t="n">
-        <v>15.1006</v>
+        <v>15.29</v>
       </c>
       <c r="F6" t="n">
-        <v>8.6853</v>
+        <v>8.693199999999999</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5114</v>
+        <v>0.4998</v>
       </c>
       <c r="H6" t="n">
-        <v>38.5</v>
+        <v>40.2</v>
       </c>
     </row>
     <row r="7">
@@ -3125,19 +3169,19 @@
         <v>6</v>
       </c>
       <c r="D7" t="n">
-        <v>7.712</v>
+        <v>7.7191</v>
       </c>
       <c r="E7" t="n">
-        <v>14.6217</v>
+        <v>14.6189</v>
       </c>
       <c r="F7" t="n">
-        <v>7.8907</v>
+        <v>7.898</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1915</v>
+        <v>0.197</v>
       </c>
       <c r="H7" t="n">
-        <v>22.5</v>
+        <v>22.7</v>
       </c>
     </row>
     <row r="8">
@@ -3155,19 +3199,19 @@
         <v>6</v>
       </c>
       <c r="D8" t="n">
-        <v>7.5763</v>
+        <v>7.7584</v>
       </c>
       <c r="E8" t="n">
-        <v>5.0923</v>
+        <v>5.3374</v>
       </c>
       <c r="F8" t="n">
-        <v>9.3596</v>
+        <v>9.5617</v>
       </c>
       <c r="G8" t="n">
-        <v>0.3911</v>
+        <v>0.3864</v>
       </c>
       <c r="H8" t="n">
-        <v>65.8</v>
+        <v>67.3</v>
       </c>
     </row>
     <row r="9">
@@ -3185,19 +3229,19 @@
         <v>6</v>
       </c>
       <c r="D9" t="n">
-        <v>23.1365</v>
+        <v>23.1472</v>
       </c>
       <c r="E9" t="n">
-        <v>20.0167</v>
+        <v>20.27</v>
       </c>
       <c r="F9" t="n">
-        <v>24.8016</v>
+        <v>24.8745</v>
       </c>
       <c r="G9" t="n">
-        <v>0.543</v>
+        <v>0.5249</v>
       </c>
       <c r="H9" t="n">
-        <v>52.3</v>
+        <v>53.5</v>
       </c>
     </row>
     <row r="10">
@@ -3212,22 +3256,22 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="D10" t="n">
-        <v>19.472</v>
+        <v>16.9568</v>
       </c>
       <c r="E10" t="n">
-        <v>20.9921</v>
+        <v>17.1382</v>
       </c>
       <c r="F10" t="n">
-        <v>20.2435</v>
+        <v>17.7511</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3525</v>
+        <v>0.3653</v>
       </c>
       <c r="H10" t="n">
-        <v>32</v>
+        <v>60.8</v>
       </c>
     </row>
   </sheetData>
